--- a/PLAFT/Desarrollo/Minorista_regulado/Documentacion/diccionario_variables.xlsx
+++ b/PLAFT/Desarrollo/Minorista_regulado/Documentacion/diccionario_variables.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/PLAFT/Desarrollo/Minorista_regulado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/PLAFT/Desarrollo/Minorista_regulado/Documentacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="11_D4685D6D51B00C8EC238E11B3E10620A61868518" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{401890F3-A291-4395-B8DF-473F2906D5F8}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="11_D4685D6D51B00C8EC238E11B3E10620A61868518" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE5F03B4-A9A4-442C-ADF0-5AC48C97D8D6}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" xr2:uid="{953A7621-5D67-4682-9C09-2CA2A8669DE6}"/>
+    <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{953A7621-5D67-4682-9C09-2CA2A8669DE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Diccionario" sheetId="2" r:id="rId1"/>
-    <sheet name="Variables finales" sheetId="4" r:id="rId2"/>
-    <sheet name="Modelo" sheetId="5" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="6" r:id="rId2"/>
+    <sheet name="Variables finales" sheetId="4" r:id="rId3"/>
+    <sheet name="Modelo" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="936">
   <si>
     <t>TABLA AGREGADA ALERTAS PLAFT - AWS</t>
   </si>
@@ -2819,13 +2820,43 @@
   </si>
   <si>
     <t>Cantidad de trx sin envio la exterior en los ultimos 12 meses</t>
+  </si>
+  <si>
+    <t>node_id</t>
+  </si>
+  <si>
+    <t>comunidad</t>
+  </si>
+  <si>
+    <t>monto_enviado</t>
+  </si>
+  <si>
+    <t>monto_recibido</t>
+  </si>
+  <si>
+    <t>monto_total</t>
+  </si>
+  <si>
+    <t>n_vecinos_ros</t>
+  </si>
+  <si>
+    <t>n_vecinos_alerta</t>
+  </si>
+  <si>
+    <t>n_ros</t>
+  </si>
+  <si>
+    <t>distancia_ros</t>
+  </si>
+  <si>
+    <t>NaN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2915,6 +2946,17 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="14">
@@ -3151,7 +3193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3224,6 +3266,34 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3269,34 +3339,12 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3687,24 +3735,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.5" customHeight="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1">
-      <c r="A2" s="31"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="33"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="5" t="s">
@@ -3712,12 +3760,12 @@
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="36"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="46"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
@@ -3725,25 +3773,25 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="39"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="42"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="52"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8" t="s">
@@ -9130,7 +9178,7 @@
       <c r="G300" s="2"/>
     </row>
     <row r="301" spans="1:7" ht="15" thickBot="1">
-      <c r="C301" s="43" t="s">
+      <c r="C301" s="28" t="s">
         <v>248</v>
       </c>
       <c r="F301" t="str">
@@ -9175,6 +9223,637 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1C4D4A-4FD2-4377-ADA0-4C4CAF349F18}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="31.5">
+      <c r="A1" s="53" t="s">
+        <v>926</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>927</v>
+      </c>
+      <c r="C1" s="53" t="s">
+        <v>928</v>
+      </c>
+      <c r="D1" s="53" t="s">
+        <v>929</v>
+      </c>
+      <c r="E1" s="53" t="s">
+        <v>930</v>
+      </c>
+      <c r="F1" s="53" t="s">
+        <v>931</v>
+      </c>
+      <c r="G1" s="53" t="s">
+        <v>932</v>
+      </c>
+      <c r="H1" s="53" t="s">
+        <v>933</v>
+      </c>
+      <c r="I1" s="53" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="54">
+        <v>17288827</v>
+      </c>
+      <c r="B2" s="54">
+        <v>1</v>
+      </c>
+      <c r="C2" s="54">
+        <v>11250000</v>
+      </c>
+      <c r="D2" s="54">
+        <v>53.1</v>
+      </c>
+      <c r="E2" s="54">
+        <v>11250053.1</v>
+      </c>
+      <c r="F2" s="54">
+        <v>0</v>
+      </c>
+      <c r="G2" s="54">
+        <v>2</v>
+      </c>
+      <c r="H2" s="54">
+        <v>206</v>
+      </c>
+      <c r="I2" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="54">
+        <v>16697325</v>
+      </c>
+      <c r="B3" s="54">
+        <v>1</v>
+      </c>
+      <c r="C3" s="54">
+        <v>0</v>
+      </c>
+      <c r="D3" s="54">
+        <v>9894997.2599999998</v>
+      </c>
+      <c r="E3" s="54">
+        <v>9894997.2599999998</v>
+      </c>
+      <c r="F3" s="54">
+        <v>0</v>
+      </c>
+      <c r="G3" s="54">
+        <v>1</v>
+      </c>
+      <c r="H3" s="54">
+        <v>206</v>
+      </c>
+      <c r="I3" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="54">
+        <v>15608422</v>
+      </c>
+      <c r="B4" s="54">
+        <v>3692</v>
+      </c>
+      <c r="C4" s="54">
+        <v>3199660.65</v>
+      </c>
+      <c r="D4" s="54">
+        <v>3222387</v>
+      </c>
+      <c r="E4" s="54">
+        <v>6422047.6500000004</v>
+      </c>
+      <c r="F4" s="54">
+        <v>0</v>
+      </c>
+      <c r="G4" s="54">
+        <v>2</v>
+      </c>
+      <c r="H4" s="54">
+        <v>14</v>
+      </c>
+      <c r="I4" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="54">
+        <v>17852409</v>
+      </c>
+      <c r="B5" s="54">
+        <v>20695</v>
+      </c>
+      <c r="C5" s="54">
+        <v>100800</v>
+      </c>
+      <c r="D5" s="54">
+        <v>5429035.4400000004</v>
+      </c>
+      <c r="E5" s="54">
+        <v>5529835.4400000004</v>
+      </c>
+      <c r="F5" s="54">
+        <v>0</v>
+      </c>
+      <c r="G5" s="54">
+        <v>1</v>
+      </c>
+      <c r="H5" s="54">
+        <v>209</v>
+      </c>
+      <c r="I5" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="54">
+        <v>18623610</v>
+      </c>
+      <c r="B6" s="54">
+        <v>14563</v>
+      </c>
+      <c r="C6" s="54">
+        <v>3601881</v>
+      </c>
+      <c r="D6" s="54">
+        <v>1376460</v>
+      </c>
+      <c r="E6" s="54">
+        <v>4978341</v>
+      </c>
+      <c r="F6" s="54">
+        <v>0</v>
+      </c>
+      <c r="G6" s="54">
+        <v>0</v>
+      </c>
+      <c r="H6" s="54">
+        <v>0</v>
+      </c>
+      <c r="I6" s="54" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="54">
+        <v>16671386</v>
+      </c>
+      <c r="B7" s="54">
+        <v>1</v>
+      </c>
+      <c r="C7" s="54">
+        <v>3705966.81</v>
+      </c>
+      <c r="D7" s="54">
+        <v>530960.49</v>
+      </c>
+      <c r="E7" s="54">
+        <v>4236927.3</v>
+      </c>
+      <c r="F7" s="54">
+        <v>0</v>
+      </c>
+      <c r="G7" s="54">
+        <v>1</v>
+      </c>
+      <c r="H7" s="54">
+        <v>206</v>
+      </c>
+      <c r="I7" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="54">
+        <v>22223437</v>
+      </c>
+      <c r="B8" s="54">
+        <v>1</v>
+      </c>
+      <c r="C8" s="54">
+        <v>16120.8</v>
+      </c>
+      <c r="D8" s="54">
+        <v>3489850.35</v>
+      </c>
+      <c r="E8" s="54">
+        <v>3505971.15</v>
+      </c>
+      <c r="F8" s="54">
+        <v>0</v>
+      </c>
+      <c r="G8" s="54">
+        <v>1</v>
+      </c>
+      <c r="H8" s="54">
+        <v>206</v>
+      </c>
+      <c r="I8" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="54">
+        <v>14214020</v>
+      </c>
+      <c r="B9" s="54">
+        <v>1</v>
+      </c>
+      <c r="C9" s="54">
+        <v>2592438.48</v>
+      </c>
+      <c r="D9" s="54">
+        <v>842843.97</v>
+      </c>
+      <c r="E9" s="54">
+        <v>3435282.45</v>
+      </c>
+      <c r="F9" s="54">
+        <v>0</v>
+      </c>
+      <c r="G9" s="54">
+        <v>1</v>
+      </c>
+      <c r="H9" s="54">
+        <v>206</v>
+      </c>
+      <c r="I9" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="54">
+        <v>21324114</v>
+      </c>
+      <c r="B10" s="54">
+        <v>1</v>
+      </c>
+      <c r="C10" s="54">
+        <v>1207703.97</v>
+      </c>
+      <c r="D10" s="54">
+        <v>1601079.57</v>
+      </c>
+      <c r="E10" s="54">
+        <v>2808783.54</v>
+      </c>
+      <c r="F10" s="54">
+        <v>0</v>
+      </c>
+      <c r="G10" s="54">
+        <v>1</v>
+      </c>
+      <c r="H10" s="54">
+        <v>206</v>
+      </c>
+      <c r="I10" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="54">
+        <v>15351665</v>
+      </c>
+      <c r="B11" s="54">
+        <v>3</v>
+      </c>
+      <c r="C11" s="54">
+        <v>0</v>
+      </c>
+      <c r="D11" s="54">
+        <v>2727571.59</v>
+      </c>
+      <c r="E11" s="54">
+        <v>2727571.59</v>
+      </c>
+      <c r="F11" s="54">
+        <v>0</v>
+      </c>
+      <c r="G11" s="54">
+        <v>0</v>
+      </c>
+      <c r="H11" s="54">
+        <v>25</v>
+      </c>
+      <c r="I11" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="54">
+        <v>19580612</v>
+      </c>
+      <c r="B12" s="54">
+        <v>62</v>
+      </c>
+      <c r="C12" s="54">
+        <v>126000</v>
+      </c>
+      <c r="D12" s="54">
+        <v>2500656.0299999998</v>
+      </c>
+      <c r="E12" s="54">
+        <v>2626656.0299999998</v>
+      </c>
+      <c r="F12" s="54">
+        <v>0</v>
+      </c>
+      <c r="G12" s="54">
+        <v>2</v>
+      </c>
+      <c r="H12" s="54">
+        <v>80</v>
+      </c>
+      <c r="I12" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="54">
+        <v>16717648</v>
+      </c>
+      <c r="B13" s="54">
+        <v>23952</v>
+      </c>
+      <c r="C13" s="54">
+        <v>1933627.05</v>
+      </c>
+      <c r="D13" s="54">
+        <v>434800.71</v>
+      </c>
+      <c r="E13" s="54">
+        <v>2368427.7599999998</v>
+      </c>
+      <c r="F13" s="54">
+        <v>0</v>
+      </c>
+      <c r="G13" s="54">
+        <v>0</v>
+      </c>
+      <c r="H13" s="54">
+        <v>219</v>
+      </c>
+      <c r="I13" s="54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="54">
+        <v>16063224</v>
+      </c>
+      <c r="B14" s="54">
+        <v>32</v>
+      </c>
+      <c r="C14" s="54">
+        <v>18000</v>
+      </c>
+      <c r="D14" s="54">
+        <v>2318938.2000000002</v>
+      </c>
+      <c r="E14" s="54">
+        <v>2336938.2000000002</v>
+      </c>
+      <c r="F14" s="54">
+        <v>0</v>
+      </c>
+      <c r="G14" s="54">
+        <v>1</v>
+      </c>
+      <c r="H14" s="54">
+        <v>109</v>
+      </c>
+      <c r="I14" s="54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="54">
+        <v>21792783</v>
+      </c>
+      <c r="B15" s="54">
+        <v>137</v>
+      </c>
+      <c r="C15" s="54">
+        <v>1585149.3</v>
+      </c>
+      <c r="D15" s="54">
+        <v>738000</v>
+      </c>
+      <c r="E15" s="54">
+        <v>2323149.2999999998</v>
+      </c>
+      <c r="F15" s="54">
+        <v>0</v>
+      </c>
+      <c r="G15" s="54">
+        <v>0</v>
+      </c>
+      <c r="H15" s="54">
+        <v>201</v>
+      </c>
+      <c r="I15" s="54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="54">
+        <v>20570207</v>
+      </c>
+      <c r="B16" s="54">
+        <v>745</v>
+      </c>
+      <c r="C16" s="54">
+        <v>2207700</v>
+      </c>
+      <c r="D16" s="54">
+        <v>10620</v>
+      </c>
+      <c r="E16" s="54">
+        <v>2218320</v>
+      </c>
+      <c r="F16" s="54">
+        <v>1</v>
+      </c>
+      <c r="G16" s="54">
+        <v>1</v>
+      </c>
+      <c r="H16" s="54">
+        <v>92</v>
+      </c>
+      <c r="I16" s="54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="54">
+        <v>20395241</v>
+      </c>
+      <c r="B17" s="54">
+        <v>53</v>
+      </c>
+      <c r="C17" s="54">
+        <v>1742151.42</v>
+      </c>
+      <c r="D17" s="54">
+        <v>319590</v>
+      </c>
+      <c r="E17" s="54">
+        <v>2061741.42</v>
+      </c>
+      <c r="F17" s="54">
+        <v>0</v>
+      </c>
+      <c r="G17" s="54">
+        <v>1</v>
+      </c>
+      <c r="H17" s="54">
+        <v>47</v>
+      </c>
+      <c r="I17" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="54">
+        <v>19176781</v>
+      </c>
+      <c r="B18" s="54">
+        <v>63</v>
+      </c>
+      <c r="C18" s="54">
+        <v>2019613.05</v>
+      </c>
+      <c r="D18" s="54">
+        <v>0</v>
+      </c>
+      <c r="E18" s="54">
+        <v>2019613.05</v>
+      </c>
+      <c r="F18" s="54">
+        <v>0</v>
+      </c>
+      <c r="G18" s="54">
+        <v>1</v>
+      </c>
+      <c r="H18" s="54">
+        <v>83</v>
+      </c>
+      <c r="I18" s="54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="54">
+        <v>20610895</v>
+      </c>
+      <c r="B19" s="54">
+        <v>75</v>
+      </c>
+      <c r="C19" s="54">
+        <v>1774757.34</v>
+      </c>
+      <c r="D19" s="54">
+        <v>222739.83</v>
+      </c>
+      <c r="E19" s="54">
+        <v>1997497.17</v>
+      </c>
+      <c r="F19" s="54">
+        <v>0</v>
+      </c>
+      <c r="G19" s="54">
+        <v>1</v>
+      </c>
+      <c r="H19" s="54">
+        <v>79</v>
+      </c>
+      <c r="I19" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="54">
+        <v>16878937</v>
+      </c>
+      <c r="B20" s="54">
+        <v>38</v>
+      </c>
+      <c r="C20" s="54">
+        <v>163895.4</v>
+      </c>
+      <c r="D20" s="54">
+        <v>1701728.82</v>
+      </c>
+      <c r="E20" s="54">
+        <v>1865624.22</v>
+      </c>
+      <c r="F20" s="54">
+        <v>0</v>
+      </c>
+      <c r="G20" s="54">
+        <v>1</v>
+      </c>
+      <c r="H20" s="54">
+        <v>23</v>
+      </c>
+      <c r="I20" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="54">
+        <v>21706791</v>
+      </c>
+      <c r="B21" s="54">
+        <v>31</v>
+      </c>
+      <c r="C21" s="54">
+        <v>1143381.6000000001</v>
+      </c>
+      <c r="D21" s="54">
+        <v>720110.7</v>
+      </c>
+      <c r="E21" s="54">
+        <v>1863492.3</v>
+      </c>
+      <c r="F21" s="54">
+        <v>1</v>
+      </c>
+      <c r="G21" s="54">
+        <v>1</v>
+      </c>
+      <c r="H21" s="54">
+        <v>242</v>
+      </c>
+      <c r="I21" s="54">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DCCAE6-0E9B-4753-90E8-43F48446DEA8}">
   <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -9199,230 +9878,230 @@
       <c r="A2" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="B2" s="43" t="str">
+      <c r="B2" s="28" t="str">
         <f>VLOOKUP(A2,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Cantidad de cargos  en los últimos 3 meses.</v>
       </c>
-      <c r="C2" s="43"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1">
       <c r="A3" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="43" t="str">
+      <c r="B3" s="28" t="str">
         <f>VLOOKUP(A3,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Monto de pasivos del cliente en moneda de tipo soles.</v>
       </c>
-      <c r="C3" s="43"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" thickBot="1">
       <c r="A4" s="12" t="s">
         <v>891</v>
       </c>
-      <c r="B4" s="43" t="str">
+      <c r="B4" s="28" t="str">
         <f>VLOOKUP(A4,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v> Esta variable calcula la relación entre el pasivo total en soles y los ingresos totales (abonos) en los últimos 6 meses. Es un indicador de la capacidad de la empresa para cubrir sus pasivos con los ingresos generados.</v>
       </c>
-      <c r="C4" s="43"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" ht="15" thickBot="1">
       <c r="A5" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="B5" s="43" t="str">
+      <c r="B5" s="28" t="str">
         <f>VLOOKUP(A5,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Promedio mensual de cantidad de abonos totales en los últimos 3 meses.</v>
       </c>
-      <c r="C5" s="43"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3" ht="15" thickBot="1">
       <c r="A6" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="B6" s="43" t="str">
+      <c r="B6" s="28" t="str">
         <f>VLOOKUP(A6,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Monto total de abonos en efectivo en los últimos 6 meses.</v>
       </c>
-      <c r="C6" s="43"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="15" thickBot="1">
       <c r="A7" s="12" t="s">
         <v>856</v>
       </c>
-      <c r="B7" s="43" t="str">
+      <c r="B7" s="28" t="str">
         <f>VLOOKUP(A7,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Años de relación comercial con el cliente</v>
       </c>
-      <c r="C7" s="43"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:3" ht="15" thickBot="1">
       <c r="A8" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="B8" s="43" t="str">
+      <c r="B8" s="28" t="str">
         <f>VLOOKUP(A8,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Total egresado en efectivo en los ultimos 6 meses.</v>
       </c>
-      <c r="C8" s="43"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="37" t="s">
         <v>918</v>
       </c>
-      <c r="B9" s="43" t="str">
+      <c r="B9" s="28" t="str">
         <f>VLOOKUP(A9,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Este ratio mide la aceleración o desaceleración de los egresos (cargos) en el último mes en comparación con el promedio mensual de los últimos 6 meses. Es útil para identificar cambios recientes en el comportamiento de egresos.</v>
       </c>
-      <c r="C9" s="43"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1">
       <c r="A10" s="12" t="s">
         <v>670</v>
       </c>
-      <c r="B10" s="43" t="str">
+      <c r="B10" s="28" t="str">
         <f>VLOOKUP(A10,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Número de meses, dentro de los últimos 12 meses, en que no se registraron cargos.</v>
       </c>
-      <c r="C10" s="43"/>
+      <c r="C10" s="28"/>
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1">
       <c r="A11" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B11" s="43" t="str">
+      <c r="B11" s="28" t="str">
         <f>VLOOKUP(A11,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Cantidad total de alertas históricas relacionadas al cliente.</v>
       </c>
-      <c r="C11" s="43"/>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1">
       <c r="A12" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="B12" s="43" t="str">
+      <c r="B12" s="28" t="str">
         <f>VLOOKUP(A12,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Ratio de cantidad de abonos en efectivo respecto a la cantidad total de abonos, considerando ambos valores acumulados en los últimos 3 meses</v>
       </c>
-      <c r="C12" s="43"/>
+      <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1">
       <c r="A13" s="12" t="s">
         <v>643</v>
       </c>
-      <c r="B13" s="43" t="str">
+      <c r="B13" s="28" t="str">
         <f>VLOOKUP(A13,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Promedio de los cargos totales en los últimos 3 meses.</v>
       </c>
-      <c r="C13" s="43"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1">
       <c r="A14" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="B14" s="43" t="str">
+      <c r="B14" s="28" t="str">
         <f>VLOOKUP(A14,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Porcentaje del monto de cargos realizados en efectivo sobre el total de cargos del último mes.</v>
       </c>
-      <c r="C14" s="43"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:3" ht="15" thickBot="1">
       <c r="A15" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="B15" s="43" t="str">
+      <c r="B15" s="28" t="str">
         <f>VLOOKUP(A15,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Ratio de cantida de abonos en efectivo respecto a la cantidad total de abonos, considerando ambos valores acumulados en el último mes.</v>
       </c>
-      <c r="C15" s="43"/>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1">
       <c r="A16" s="12" t="s">
         <v>894</v>
       </c>
-      <c r="B16" s="43" t="str">
+      <c r="B16" s="28" t="str">
         <f>VLOOKUP(A16,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Esta variable calcula la relación entre la cantidad de reportes de operaciones sospechosas (ROS) históricos y el número total de transacciones de egresos en los últimos 3 meses. Es un indicador de riesgo asociado a las operaciones recientes.</v>
       </c>
-      <c r="C16" s="43"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3" ht="15" thickBot="1">
       <c r="A17" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="28" t="s">
         <v>920</v>
       </c>
-      <c r="C17" s="43"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3" ht="15" thickBot="1">
       <c r="A18" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="B18" s="43" t="str">
+      <c r="B18" s="28" t="str">
         <f>VLOOKUP(A18,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Monto total recibido desde el exterior en los últimos 12 meses.</v>
       </c>
-      <c r="C18" s="43"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1">
       <c r="A19" s="12" t="s">
         <v>895</v>
       </c>
-      <c r="B19" s="43" t="str">
+      <c r="B19" s="28" t="str">
         <f>VLOOKUP(A19,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Esta variable mide la proporción de ingresos provenientes del exterior en relación con los ingresos totales (abonos) en los últimos 12 meses. Es un indicador de la dependencia de la empresa en ingresos internacionales.</v>
       </c>
-      <c r="C19" s="43"/>
+      <c r="C19" s="28"/>
     </row>
     <row r="20" spans="1:3" ht="15" thickBot="1">
       <c r="A20" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="B20" s="43" t="str">
+      <c r="B20" s="28" t="str">
         <f>VLOOKUP(A20,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Monto máximo de egreso en un solo mes de una o más contrapartes dentro de los últimos 12 meses.</v>
       </c>
-      <c r="C20" s="43"/>
+      <c r="C20" s="28"/>
     </row>
     <row r="21" spans="1:3" ht="15" thickBot="1">
       <c r="A21" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="B21" s="43" t="str">
+      <c r="B21" s="28" t="str">
         <f>VLOOKUP(A21,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Promedio mensual de egresos hacia contrapartes en los últimos 12 meses.</v>
       </c>
-      <c r="C21" s="43"/>
+      <c r="C21" s="28"/>
     </row>
     <row r="22" spans="1:3" ht="15" thickBot="1">
       <c r="A22" s="12" t="s">
         <v>721</v>
       </c>
-      <c r="B22" s="43" t="str">
+      <c r="B22" s="28" t="str">
         <f>VLOOKUP(A22,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Monto total enviado al exterior en los últimos 12 meses.</v>
       </c>
-      <c r="C22" s="43"/>
+      <c r="C22" s="28"/>
     </row>
     <row r="23" spans="1:3" ht="15" thickBot="1">
       <c r="A23" s="27" t="s">
         <v>895</v>
       </c>
-      <c r="B23" s="43" t="str">
+      <c r="B23" s="28" t="str">
         <f>VLOOKUP(A23,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Esta variable mide la proporción de ingresos provenientes del exterior en relación con los ingresos totales (abonos) en los últimos 12 meses. Es un indicador de la dependencia de la empresa en ingresos internacionales.</v>
       </c>
-      <c r="C23" s="43"/>
+      <c r="C23" s="28"/>
     </row>
     <row r="24" spans="1:3" ht="15" thickBot="1">
       <c r="A24" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B24" s="43" t="str">
+      <c r="B24" s="28" t="str">
         <f>VLOOKUP(A24,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Número total de ROS en los que el cliente ha estado involucrado.</v>
       </c>
-      <c r="C24" s="43"/>
+      <c r="C24" s="28"/>
     </row>
     <row r="25" spans="1:3" ht="15" thickBot="1">
       <c r="A25" s="12" t="s">
@@ -9431,85 +10110,85 @@
       <c r="B25" t="s">
         <v>925</v>
       </c>
-      <c r="C25" s="43"/>
+      <c r="C25" s="28"/>
     </row>
     <row r="26" spans="1:3" ht="15" thickBot="1">
       <c r="A26" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="43" t="str">
+      <c r="B26" s="28" t="str">
         <f>VLOOKUP(A26,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Indicador si el cliente ha generado alguna alerta PLAFT en los últimos 12 meses.</v>
       </c>
-      <c r="C26" s="43"/>
+      <c r="C26" s="28"/>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1">
       <c r="A27" s="12" t="s">
         <v>850</v>
       </c>
-      <c r="B27" s="43" t="str">
+      <c r="B27" s="28" t="str">
         <f>VLOOKUP(A27,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Si el monto total abonos del último mes es mayor al monto promedio total abonos de los últimos 5 meses coloco 1, caso contrario 0</v>
       </c>
-      <c r="C27" s="43"/>
+      <c r="C27" s="28"/>
     </row>
     <row r="28" spans="1:3" ht="15" thickBot="1">
       <c r="A28" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="B28" s="43" t="str">
+      <c r="B28" s="28" t="str">
         <f>VLOOKUP(A28,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Promedio mensual de ingresos provenientes de suscontrapartes en los últimos 12 meses.</v>
       </c>
-      <c r="C28" s="43"/>
+      <c r="C28" s="28"/>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1">
       <c r="A29" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B29" s="43" t="str">
+      <c r="B29" s="28" t="str">
         <f>VLOOKUP(A29,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Número total de noticias negativas registradas del cliente.</v>
       </c>
-      <c r="C29" s="43"/>
+      <c r="C29" s="28"/>
     </row>
     <row r="30" spans="1:3" ht="15" thickBot="1">
       <c r="A30" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="28" t="s">
         <v>924</v>
       </c>
-      <c r="C30" s="43"/>
+      <c r="C30" s="28"/>
     </row>
     <row r="31" spans="1:3" ht="15" thickBot="1">
       <c r="A31" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="43" t="str">
+      <c r="B31" s="28" t="str">
         <f>VLOOKUP(A31,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Monto de facturación declarado del cliente, según SUNAT</v>
       </c>
-      <c r="C31" s="43"/>
+      <c r="C31" s="28"/>
     </row>
     <row r="32" spans="1:3" ht="15" thickBot="1">
       <c r="A32" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="43" t="s">
+      <c r="B32" s="28" t="s">
         <v>921</v>
       </c>
-      <c r="C32" s="43"/>
+      <c r="C32" s="28"/>
     </row>
     <row r="33" spans="1:3" ht="15" thickBot="1">
       <c r="A33" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="43" t="str">
+      <c r="B33" s="28" t="str">
         <f>VLOOKUP(A33,Diccionario!$C$7:$F$300,4,FALSE)</f>
         <v>Identificador del sector asignado al cliente</v>
       </c>
-      <c r="C33" s="43"/>
+      <c r="C33" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9517,7 +10196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374C8810-FB16-41CA-85D2-70D0F0D810E2}">
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -9531,33 +10210,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="29" t="s">
         <v>897</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="29" t="s">
         <v>898</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="30" t="s">
         <v>899</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="30" t="s">
         <v>900</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="30" t="s">
         <v>901</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="30" t="s">
         <v>902</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C2" s="15" t="s">
@@ -9569,16 +10248,16 @@
       <c r="E2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="48"/>
+      <c r="F2" s="33"/>
       <c r="G2" s="13" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C3" s="15" t="s">
@@ -9598,10 +10277,10 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -9621,10 +10300,10 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C5" s="15" t="s">
@@ -9644,10 +10323,10 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="32" t="s">
         <v>909</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -9659,16 +10338,16 @@
       <c r="E6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="48"/>
+      <c r="F6" s="33"/>
       <c r="G6" s="13" t="s">
         <v>912</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C7" s="15" t="s">
@@ -9680,16 +10359,16 @@
       <c r="E7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="48"/>
+      <c r="F7" s="33"/>
       <c r="G7" s="13" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -9701,16 +10380,16 @@
       <c r="E8" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="49" t="s">
+      <c r="F8" s="33"/>
+      <c r="G8" s="34" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C9" s="15" t="s">
@@ -9722,37 +10401,37 @@
       <c r="E9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="48"/>
+      <c r="F9" s="33"/>
       <c r="G9" s="15" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="32" t="s">
         <v>904</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="35" t="s">
         <v>492</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="35" t="s">
         <v>493</v>
       </c>
-      <c r="E10" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="F10" s="48"/>
+      <c r="E10" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="33"/>
       <c r="G10" s="15" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C11" s="15" t="s">
@@ -9764,16 +10443,16 @@
       <c r="E11" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="48"/>
+      <c r="F11" s="33"/>
       <c r="G11" s="15" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C12" s="15" t="s">
@@ -9785,16 +10464,16 @@
       <c r="E12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="48"/>
+      <c r="F12" s="33"/>
       <c r="G12" s="15" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C13" s="15" t="s">
@@ -9806,16 +10485,16 @@
       <c r="E13" s="11" t="s">
         <v>913</v>
       </c>
-      <c r="F13" s="48"/>
+      <c r="F13" s="33"/>
       <c r="G13" s="15" t="s">
         <v>914</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C14" s="15" t="s">
@@ -9827,16 +10506,16 @@
       <c r="E14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="48"/>
+      <c r="F14" s="33"/>
       <c r="G14" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C15" s="15" t="s">
@@ -9848,16 +10527,16 @@
       <c r="E15" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="48"/>
+      <c r="F15" s="33"/>
       <c r="G15" s="15" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C16" s="15" t="s">
@@ -9869,16 +10548,16 @@
       <c r="E16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="48"/>
+      <c r="F16" s="33"/>
       <c r="G16" s="15" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C17" s="15" t="s">
@@ -9890,16 +10569,16 @@
       <c r="E17" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="48"/>
+      <c r="F17" s="33"/>
       <c r="G17" s="15" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C18" s="15" t="s">
@@ -9911,16 +10590,16 @@
       <c r="E18" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F18" s="48"/>
+      <c r="F18" s="33"/>
       <c r="G18" s="15" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C19" s="15" t="s">
@@ -9932,16 +10611,16 @@
       <c r="E19" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="48"/>
+      <c r="F19" s="33"/>
       <c r="G19" s="15" t="s">
         <v>915</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C20" s="15" t="s">
@@ -9953,16 +10632,16 @@
       <c r="E20" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F20" s="48"/>
+      <c r="F20" s="33"/>
       <c r="G20" s="15" t="s">
         <v>916</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C21" s="15" t="s">
@@ -9974,16 +10653,16 @@
       <c r="E21" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="48"/>
+      <c r="F21" s="33"/>
       <c r="G21" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C22" s="15" t="s">
@@ -9995,16 +10674,16 @@
       <c r="E22" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="48"/>
+      <c r="F22" s="33"/>
       <c r="G22" s="15" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C23" s="15" t="s">
@@ -10016,16 +10695,16 @@
       <c r="E23" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="48"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="15" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C24" s="15" t="s">
@@ -10037,16 +10716,16 @@
       <c r="E24" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="48"/>
+      <c r="F24" s="33"/>
       <c r="G24" s="15" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C25" s="15" t="s">
@@ -10058,16 +10737,16 @@
       <c r="E25" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F25" s="48"/>
+      <c r="F25" s="33"/>
       <c r="G25" s="15" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C26" s="15" t="s">
@@ -10079,16 +10758,16 @@
       <c r="E26" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="48"/>
+      <c r="F26" s="33"/>
       <c r="G26" s="15" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C27" s="13" t="s">
@@ -10100,16 +10779,16 @@
       <c r="E27" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="48"/>
+      <c r="F27" s="33"/>
       <c r="G27" s="13" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="46" t="s">
+      <c r="A28" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C28" s="13" t="s">
@@ -10121,16 +10800,16 @@
       <c r="E28" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="48"/>
+      <c r="F28" s="33"/>
       <c r="G28" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C29" s="13" t="s">
@@ -10142,16 +10821,16 @@
       <c r="E29" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="F29" s="48"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="46" t="s">
+      <c r="A30" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C30" s="13" t="s">
@@ -10163,16 +10842,16 @@
       <c r="E30" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F30" s="48"/>
+      <c r="F30" s="33"/>
       <c r="G30" s="13" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C31" s="13" t="s">
@@ -10184,16 +10863,16 @@
       <c r="E31" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="F31" s="48"/>
+      <c r="F31" s="33"/>
       <c r="G31" s="13" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C32" s="13" t="s">
@@ -10205,16 +10884,16 @@
       <c r="E32" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="48"/>
+      <c r="F32" s="33"/>
       <c r="G32" s="13" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C33" s="13" t="s">
@@ -10226,16 +10905,16 @@
       <c r="E33" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="48"/>
+      <c r="F33" s="33"/>
       <c r="G33" s="13" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="46" t="s">
+      <c r="A34" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B34" s="47" t="s">
+      <c r="B34" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C34" s="13" t="s">
@@ -10247,16 +10926,16 @@
       <c r="E34" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="F34" s="48"/>
+      <c r="F34" s="33"/>
       <c r="G34" s="13" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="46" t="s">
+      <c r="A35" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B35" s="47" t="s">
+      <c r="B35" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C35" s="13" t="s">
@@ -10268,16 +10947,16 @@
       <c r="E35" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="F35" s="48"/>
+      <c r="F35" s="33"/>
       <c r="G35" s="13" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="46" t="s">
+      <c r="A36" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="B36" s="47" t="s">
+      <c r="B36" s="32" t="s">
         <v>904</v>
       </c>
       <c r="C36" s="13" t="s">
@@ -10289,7 +10968,7 @@
       <c r="E36" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F36" s="48"/>
+      <c r="F36" s="33"/>
       <c r="G36" s="13" t="s">
         <v>919</v>
       </c>

--- a/PLAFT/Desarrollo/Minorista_regulado/Documentacion/diccionario_variables.xlsx
+++ b/PLAFT/Desarrollo/Minorista_regulado/Documentacion/diccionario_variables.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/PLAFT/Desarrollo/Minorista_regulado/Documentacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="11_D4685D6D51B00C8EC238E11B3E10620A61868518" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE5F03B4-A9A4-442C-ADF0-5AC48C97D8D6}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="11_D4685D6D51B00C8EC238E11B3E10620A61868518" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF6E9151-AACD-4B32-B295-0F5F3626D1D9}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{953A7621-5D67-4682-9C09-2CA2A8669DE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Diccionario" sheetId="2" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="6" r:id="rId2"/>
-    <sheet name="Variables finales" sheetId="4" r:id="rId3"/>
-    <sheet name="Modelo" sheetId="5" r:id="rId4"/>
+    <sheet name="Variables finales" sheetId="4" r:id="rId2"/>
+    <sheet name="Modelo" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="927">
   <si>
     <t>TABLA AGREGADA ALERTAS PLAFT - AWS</t>
   </si>
@@ -2807,9 +2806,6 @@
     <t>Ratio que mide la concentración de egresos hacia la principal contraparte. Se calcula como el promedio mensual de egresos hacia contrapartes en los últimos 12 meses respecto al monto total de cargos en los últimos 6 meses. Un valor alto indica que el cliente canaliza la mayoría de sus salidas de dinero hacia un único destinatario.</t>
   </si>
   <si>
-    <t>Conteo de transacciones sin envío al exterior en los últimos 12 meses</t>
-  </si>
-  <si>
     <t>rat_egr_ext_x_egr_tot_12m</t>
   </si>
   <si>
@@ -2822,41 +2818,17 @@
     <t>Cantidad de trx sin envio la exterior en los ultimos 12 meses</t>
   </si>
   <si>
-    <t>node_id</t>
-  </si>
-  <si>
-    <t>comunidad</t>
-  </si>
-  <si>
-    <t>monto_enviado</t>
-  </si>
-  <si>
-    <t>monto_recibido</t>
-  </si>
-  <si>
-    <t>monto_total</t>
-  </si>
-  <si>
-    <t>n_vecinos_ros</t>
-  </si>
-  <si>
-    <t>n_vecinos_alerta</t>
-  </si>
-  <si>
-    <t>n_ros</t>
-  </si>
-  <si>
-    <t>distancia_ros</t>
-  </si>
-  <si>
-    <t>NaN</t>
+    <t>Falta</t>
+  </si>
+  <si>
+    <t>Ord</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2947,19 +2919,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="7"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3038,8 +2999,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -3189,11 +3156,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3294,6 +3272,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3339,12 +3321,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3735,24 +3712,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="42"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" thickBot="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="45"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="5" t="s">
@@ -3760,12 +3737,12 @@
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
@@ -3773,25 +3750,25 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="49"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="51"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="52"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="54"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8" t="s">
@@ -9178,6 +9155,9 @@
       <c r="G300" s="2"/>
     </row>
     <row r="301" spans="1:7" ht="15" thickBot="1">
+      <c r="A301" s="4">
+        <v>306</v>
+      </c>
       <c r="C301" s="28" t="s">
         <v>248</v>
       </c>
@@ -9187,14 +9167,17 @@
       </c>
     </row>
     <row r="302" spans="1:7">
+      <c r="A302" s="4">
+        <v>307</v>
+      </c>
       <c r="B302" s="3" t="s">
         <v>889</v>
       </c>
       <c r="C302" s="27" t="s">
+        <v>921</v>
+      </c>
+      <c r="F302" s="2" t="s">
         <v>922</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -9223,980 +9206,522 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1C4D4A-4FD2-4377-ADA0-4C4CAF349F18}">
-  <dimension ref="A1:I21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DCCAE6-0E9B-4753-90E8-43F48446DEA8}">
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74" customWidth="1"/>
+    <col min="3" max="3" width="104.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.5">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="10" t="s">
         <v>926</v>
       </c>
-      <c r="B1" s="53" t="s">
-        <v>927</v>
-      </c>
-      <c r="C1" s="53" t="s">
-        <v>928</v>
-      </c>
-      <c r="D1" s="53" t="s">
-        <v>929</v>
-      </c>
-      <c r="E1" s="53" t="s">
-        <v>930</v>
-      </c>
-      <c r="F1" s="53" t="s">
-        <v>931</v>
-      </c>
-      <c r="G1" s="53" t="s">
-        <v>932</v>
-      </c>
-      <c r="H1" s="53" t="s">
-        <v>933</v>
-      </c>
-      <c r="I1" s="53" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="54">
-        <v>17288827</v>
-      </c>
-      <c r="B2" s="54">
+      <c r="B1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" thickBot="1">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="C2" s="54">
-        <v>11250000</v>
-      </c>
-      <c r="D2" s="54">
-        <v>53.1</v>
-      </c>
-      <c r="E2" s="54">
-        <v>11250053.1</v>
-      </c>
-      <c r="F2" s="54">
-        <v>0</v>
-      </c>
-      <c r="G2" s="54">
+      <c r="B2" s="55" t="s">
+        <v>559</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>560</v>
+      </c>
+      <c r="D2" s="28"/>
+      <c r="E2">
+        <v>0.50809879999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickBot="1">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="H2" s="54">
-        <v>206</v>
-      </c>
-      <c r="I2" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="54">
-        <v>16697325</v>
-      </c>
-      <c r="B3" s="54">
-        <v>1</v>
-      </c>
-      <c r="C3" s="54">
-        <v>0</v>
-      </c>
-      <c r="D3" s="54">
-        <v>9894997.2599999998</v>
-      </c>
-      <c r="E3" s="54">
-        <v>9894997.2599999998</v>
-      </c>
-      <c r="F3" s="54">
-        <v>0</v>
-      </c>
-      <c r="G3" s="54">
-        <v>1</v>
-      </c>
-      <c r="H3" s="54">
-        <v>206</v>
-      </c>
-      <c r="I3" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="54">
-        <v>15608422</v>
-      </c>
-      <c r="B4" s="54">
-        <v>3692</v>
-      </c>
-      <c r="C4" s="54">
-        <v>3199660.65</v>
-      </c>
-      <c r="D4" s="54">
-        <v>3222387</v>
-      </c>
-      <c r="E4" s="54">
-        <v>6422047.6500000004</v>
-      </c>
-      <c r="F4" s="54">
-        <v>0</v>
-      </c>
-      <c r="G4" s="54">
-        <v>2</v>
-      </c>
-      <c r="H4" s="54">
+      <c r="B3" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="28"/>
+      <c r="E3">
+        <v>0.55158819999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>891</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>877</v>
+      </c>
+      <c r="D4" s="28"/>
+      <c r="E4">
+        <v>0.66200119999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" thickBot="1">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="D5" s="28"/>
+      <c r="E5">
+        <v>0.20248437</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>494</v>
+      </c>
+      <c r="D6" s="28"/>
+      <c r="E6">
+        <v>0.50723076</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" thickBot="1">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>857</v>
+      </c>
+      <c r="D7" s="28"/>
+      <c r="E7">
+        <v>0.22907783000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" thickBot="1">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="D8" s="28"/>
+      <c r="E8">
+        <v>0.31891456000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" thickBot="1">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>918</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="D9" s="28"/>
+      <c r="E9">
+        <v>0.103008695</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>671</v>
+      </c>
+      <c r="D10" s="28"/>
+      <c r="E10">
+        <v>0.2037564</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickBot="1">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="E11">
+        <v>0.35607477999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" thickBot="1">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>461</v>
+      </c>
+      <c r="D12" s="28"/>
+      <c r="E12">
+        <v>2.6368237999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>644</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="E13">
+        <v>2.0175342999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" thickBot="1">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>656</v>
+      </c>
+      <c r="D14" s="28"/>
+      <c r="E14">
+        <v>0.118840374</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" thickBot="1">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="I4" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="54">
-        <v>17852409</v>
-      </c>
-      <c r="B5" s="54">
-        <v>20695</v>
-      </c>
-      <c r="C5" s="54">
-        <v>100800</v>
-      </c>
-      <c r="D5" s="54">
-        <v>5429035.4400000004</v>
-      </c>
-      <c r="E5" s="54">
-        <v>5529835.4400000004</v>
-      </c>
-      <c r="F5" s="54">
-        <v>0</v>
-      </c>
-      <c r="G5" s="54">
-        <v>1</v>
-      </c>
-      <c r="H5" s="54">
-        <v>209</v>
-      </c>
-      <c r="I5" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="54">
-        <v>18623610</v>
-      </c>
-      <c r="B6" s="54">
-        <v>14563</v>
-      </c>
-      <c r="C6" s="54">
-        <v>3601881</v>
-      </c>
-      <c r="D6" s="54">
-        <v>1376460</v>
-      </c>
-      <c r="E6" s="54">
-        <v>4978341</v>
-      </c>
-      <c r="F6" s="54">
-        <v>0</v>
-      </c>
-      <c r="G6" s="54">
-        <v>0</v>
-      </c>
-      <c r="H6" s="54">
-        <v>0</v>
-      </c>
-      <c r="I6" s="54" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="54">
-        <v>16671386</v>
-      </c>
-      <c r="B7" s="54">
-        <v>1</v>
-      </c>
-      <c r="C7" s="54">
-        <v>3705966.81</v>
-      </c>
-      <c r="D7" s="54">
-        <v>530960.49</v>
-      </c>
-      <c r="E7" s="54">
-        <v>4236927.3</v>
-      </c>
-      <c r="F7" s="54">
-        <v>0</v>
-      </c>
-      <c r="G7" s="54">
-        <v>1</v>
-      </c>
-      <c r="H7" s="54">
-        <v>206</v>
-      </c>
-      <c r="I7" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="54">
-        <v>22223437</v>
-      </c>
-      <c r="B8" s="54">
-        <v>1</v>
-      </c>
-      <c r="C8" s="54">
-        <v>16120.8</v>
-      </c>
-      <c r="D8" s="54">
-        <v>3489850.35</v>
-      </c>
-      <c r="E8" s="54">
-        <v>3505971.15</v>
-      </c>
-      <c r="F8" s="54">
-        <v>0</v>
-      </c>
-      <c r="G8" s="54">
-        <v>1</v>
-      </c>
-      <c r="H8" s="54">
-        <v>206</v>
-      </c>
-      <c r="I8" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="54">
-        <v>14214020</v>
-      </c>
-      <c r="B9" s="54">
-        <v>1</v>
-      </c>
-      <c r="C9" s="54">
-        <v>2592438.48</v>
-      </c>
-      <c r="D9" s="54">
-        <v>842843.97</v>
-      </c>
-      <c r="E9" s="54">
-        <v>3435282.45</v>
-      </c>
-      <c r="F9" s="54">
-        <v>0</v>
-      </c>
-      <c r="G9" s="54">
-        <v>1</v>
-      </c>
-      <c r="H9" s="54">
-        <v>206</v>
-      </c>
-      <c r="I9" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="54">
-        <v>21324114</v>
-      </c>
-      <c r="B10" s="54">
-        <v>1</v>
-      </c>
-      <c r="C10" s="54">
-        <v>1207703.97</v>
-      </c>
-      <c r="D10" s="54">
-        <v>1601079.57</v>
-      </c>
-      <c r="E10" s="54">
-        <v>2808783.54</v>
-      </c>
-      <c r="F10" s="54">
-        <v>0</v>
-      </c>
-      <c r="G10" s="54">
-        <v>1</v>
-      </c>
-      <c r="H10" s="54">
-        <v>206</v>
-      </c>
-      <c r="I10" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="54">
-        <v>15351665</v>
-      </c>
-      <c r="B11" s="54">
-        <v>3</v>
-      </c>
-      <c r="C11" s="54">
-        <v>0</v>
-      </c>
-      <c r="D11" s="54">
-        <v>2727571.59</v>
-      </c>
-      <c r="E11" s="54">
-        <v>2727571.59</v>
-      </c>
-      <c r="F11" s="54">
-        <v>0</v>
-      </c>
-      <c r="G11" s="54">
-        <v>0</v>
-      </c>
-      <c r="H11" s="54">
+      <c r="B15" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>458</v>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15">
+        <v>2.8444325999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" thickBot="1">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>894</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>887</v>
+      </c>
+      <c r="D16" s="28"/>
+      <c r="E16">
+        <v>3.5924204000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" thickBot="1">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>920</v>
+      </c>
+      <c r="D17" s="28"/>
+      <c r="E17">
+        <v>2.7962926999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" thickBot="1">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>734</v>
+      </c>
+      <c r="D18" s="28"/>
+      <c r="E18">
+        <v>0.2653201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" thickBot="1">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>885</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19">
+        <v>4.7678597000000003E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" thickBot="1">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20">
+        <v>2.2723411999999998E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" thickBot="1">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21">
+        <v>1.7494446E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" thickBot="1">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>721</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>722</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22">
+        <v>7.9125040000000008E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" thickBot="1">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>889</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>922</v>
+      </c>
+      <c r="D23" s="28"/>
+      <c r="E23">
+        <v>2.9770036E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" thickBot="1">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="28"/>
+      <c r="E24">
+        <v>3.1605243999999998E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" thickBot="1">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>896</v>
+      </c>
+      <c r="C25" t="s">
+        <v>924</v>
+      </c>
+      <c r="D25" s="28"/>
+      <c r="E25">
+        <v>1.5604318E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" thickBot="1">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="I11" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="54">
-        <v>19580612</v>
-      </c>
-      <c r="B12" s="54">
-        <v>62</v>
-      </c>
-      <c r="C12" s="54">
-        <v>126000</v>
-      </c>
-      <c r="D12" s="54">
-        <v>2500656.0299999998</v>
-      </c>
-      <c r="E12" s="54">
-        <v>2626656.0299999998</v>
-      </c>
-      <c r="F12" s="54">
-        <v>0</v>
-      </c>
-      <c r="G12" s="54">
-        <v>2</v>
-      </c>
-      <c r="H12" s="54">
-        <v>80</v>
-      </c>
-      <c r="I12" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="54">
-        <v>16717648</v>
-      </c>
-      <c r="B13" s="54">
-        <v>23952</v>
-      </c>
-      <c r="C13" s="54">
-        <v>1933627.05</v>
-      </c>
-      <c r="D13" s="54">
-        <v>434800.71</v>
-      </c>
-      <c r="E13" s="54">
-        <v>2368427.7599999998</v>
-      </c>
-      <c r="F13" s="54">
-        <v>0</v>
-      </c>
-      <c r="G13" s="54">
-        <v>0</v>
-      </c>
-      <c r="H13" s="54">
-        <v>219</v>
-      </c>
-      <c r="I13" s="54">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="54">
-        <v>16063224</v>
-      </c>
-      <c r="B14" s="54">
+      <c r="B26" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26">
+        <v>5.6675323E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" thickBot="1">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>850</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>851</v>
+      </c>
+      <c r="D27" s="28"/>
+      <c r="E27">
+        <v>3.6020955999999998E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" thickBot="1">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="D28" s="28"/>
+      <c r="E28">
+        <v>2.0265600000000002E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" thickBot="1">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="D29" s="28"/>
+      <c r="E29">
+        <v>1.3661184E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" thickBot="1">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>890</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>923</v>
+      </c>
+      <c r="D30" s="28"/>
+      <c r="E30">
+        <v>4.3424240000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" thickBot="1">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="28"/>
+      <c r="E31">
+        <v>0.65039029999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" thickBot="1">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="28"/>
+      <c r="E32">
+        <v>0.17080948000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" thickBot="1">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="C14" s="54">
-        <v>18000</v>
-      </c>
-      <c r="D14" s="54">
-        <v>2318938.2000000002</v>
-      </c>
-      <c r="E14" s="54">
-        <v>2336938.2000000002</v>
-      </c>
-      <c r="F14" s="54">
-        <v>0</v>
-      </c>
-      <c r="G14" s="54">
-        <v>1</v>
-      </c>
-      <c r="H14" s="54">
-        <v>109</v>
-      </c>
-      <c r="I14" s="54">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="54">
-        <v>21792783</v>
-      </c>
-      <c r="B15" s="54">
-        <v>137</v>
-      </c>
-      <c r="C15" s="54">
-        <v>1585149.3</v>
-      </c>
-      <c r="D15" s="54">
-        <v>738000</v>
-      </c>
-      <c r="E15" s="54">
-        <v>2323149.2999999998</v>
-      </c>
-      <c r="F15" s="54">
-        <v>0</v>
-      </c>
-      <c r="G15" s="54">
-        <v>0</v>
-      </c>
-      <c r="H15" s="54">
-        <v>201</v>
-      </c>
-      <c r="I15" s="54">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="54">
-        <v>20570207</v>
-      </c>
-      <c r="B16" s="54">
-        <v>745</v>
-      </c>
-      <c r="C16" s="54">
-        <v>2207700</v>
-      </c>
-      <c r="D16" s="54">
-        <v>10620</v>
-      </c>
-      <c r="E16" s="54">
-        <v>2218320</v>
-      </c>
-      <c r="F16" s="54">
-        <v>1</v>
-      </c>
-      <c r="G16" s="54">
-        <v>1</v>
-      </c>
-      <c r="H16" s="54">
-        <v>92</v>
-      </c>
-      <c r="I16" s="54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="54">
-        <v>20395241</v>
-      </c>
-      <c r="B17" s="54">
-        <v>53</v>
-      </c>
-      <c r="C17" s="54">
-        <v>1742151.42</v>
-      </c>
-      <c r="D17" s="54">
-        <v>319590</v>
-      </c>
-      <c r="E17" s="54">
-        <v>2061741.42</v>
-      </c>
-      <c r="F17" s="54">
-        <v>0</v>
-      </c>
-      <c r="G17" s="54">
-        <v>1</v>
-      </c>
-      <c r="H17" s="54">
-        <v>47</v>
-      </c>
-      <c r="I17" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="54">
-        <v>19176781</v>
-      </c>
-      <c r="B18" s="54">
+      <c r="B33" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="54">
-        <v>2019613.05</v>
-      </c>
-      <c r="D18" s="54">
-        <v>0</v>
-      </c>
-      <c r="E18" s="54">
-        <v>2019613.05</v>
-      </c>
-      <c r="F18" s="54">
-        <v>0</v>
-      </c>
-      <c r="G18" s="54">
-        <v>1</v>
-      </c>
-      <c r="H18" s="54">
-        <v>83</v>
-      </c>
-      <c r="I18" s="54">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="54">
-        <v>20610895</v>
-      </c>
-      <c r="B19" s="54">
-        <v>75</v>
-      </c>
-      <c r="C19" s="54">
-        <v>1774757.34</v>
-      </c>
-      <c r="D19" s="54">
-        <v>222739.83</v>
-      </c>
-      <c r="E19" s="54">
-        <v>1997497.17</v>
-      </c>
-      <c r="F19" s="54">
-        <v>0</v>
-      </c>
-      <c r="G19" s="54">
-        <v>1</v>
-      </c>
-      <c r="H19" s="54">
-        <v>79</v>
-      </c>
-      <c r="I19" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="54">
-        <v>16878937</v>
-      </c>
-      <c r="B20" s="54">
-        <v>38</v>
-      </c>
-      <c r="C20" s="54">
-        <v>163895.4</v>
-      </c>
-      <c r="D20" s="54">
-        <v>1701728.82</v>
-      </c>
-      <c r="E20" s="54">
-        <v>1865624.22</v>
-      </c>
-      <c r="F20" s="54">
-        <v>0</v>
-      </c>
-      <c r="G20" s="54">
-        <v>1</v>
-      </c>
-      <c r="H20" s="54">
-        <v>23</v>
-      </c>
-      <c r="I20" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="54">
-        <v>21706791</v>
-      </c>
-      <c r="B21" s="54">
-        <v>31</v>
-      </c>
-      <c r="C21" s="54">
-        <v>1143381.6000000001</v>
-      </c>
-      <c r="D21" s="54">
-        <v>720110.7</v>
-      </c>
-      <c r="E21" s="54">
-        <v>1863492.3</v>
-      </c>
-      <c r="F21" s="54">
-        <v>1</v>
-      </c>
-      <c r="G21" s="54">
-        <v>1</v>
-      </c>
-      <c r="H21" s="54">
-        <v>242</v>
-      </c>
-      <c r="I21" s="54">
-        <v>1</v>
+      <c r="C33" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33">
+        <v>0.13392287</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E33">
+    <sortCondition ref="A2:A33"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DCCAE6-0E9B-4753-90E8-43F48446DEA8}">
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="46.26953125" customWidth="1"/>
-    <col min="2" max="2" width="61.81640625" customWidth="1"/>
-    <col min="3" max="3" width="29.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1">
-      <c r="A2" s="12" t="s">
-        <v>559</v>
-      </c>
-      <c r="B2" s="28" t="str">
-        <f>VLOOKUP(A2,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Cantidad de cargos  en los últimos 3 meses.</v>
-      </c>
-      <c r="C2" s="28"/>
-    </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1">
-      <c r="A3" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="28" t="str">
-        <f>VLOOKUP(A3,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Monto de pasivos del cliente en moneda de tipo soles.</v>
-      </c>
-      <c r="C3" s="28"/>
-    </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1">
-      <c r="A4" s="12" t="s">
-        <v>891</v>
-      </c>
-      <c r="B4" s="28" t="str">
-        <f>VLOOKUP(A4,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v> Esta variable calcula la relación entre el pasivo total en soles y los ingresos totales (abonos) en los últimos 6 meses. Es un indicador de la capacidad de la empresa para cubrir sus pasivos con los ingresos generados.</v>
-      </c>
-      <c r="C4" s="28"/>
-    </row>
-    <row r="5" spans="1:3" ht="15" thickBot="1">
-      <c r="A5" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="B5" s="28" t="str">
-        <f>VLOOKUP(A5,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Promedio mensual de cantidad de abonos totales en los últimos 3 meses.</v>
-      </c>
-      <c r="C5" s="28"/>
-    </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1">
-      <c r="A6" s="12" t="s">
-        <v>493</v>
-      </c>
-      <c r="B6" s="28" t="str">
-        <f>VLOOKUP(A6,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Monto total de abonos en efectivo en los últimos 6 meses.</v>
-      </c>
-      <c r="C6" s="28"/>
-    </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1">
-      <c r="A7" s="12" t="s">
-        <v>856</v>
-      </c>
-      <c r="B7" s="28" t="str">
-        <f>VLOOKUP(A7,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Años de relación comercial con el cliente</v>
-      </c>
-      <c r="C7" s="28"/>
-    </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1">
-      <c r="A8" s="12" t="s">
-        <v>634</v>
-      </c>
-      <c r="B8" s="28" t="str">
-        <f>VLOOKUP(A8,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Total egresado en efectivo en los ultimos 6 meses.</v>
-      </c>
-      <c r="C8" s="28"/>
-    </row>
-    <row r="9" spans="1:3" ht="15" thickBot="1">
-      <c r="A9" s="37" t="s">
-        <v>918</v>
-      </c>
-      <c r="B9" s="28" t="str">
-        <f>VLOOKUP(A9,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Este ratio mide la aceleración o desaceleración de los egresos (cargos) en el último mes en comparación con el promedio mensual de los últimos 6 meses. Es útil para identificar cambios recientes en el comportamiento de egresos.</v>
-      </c>
-      <c r="C9" s="28"/>
-    </row>
-    <row r="10" spans="1:3" ht="15" thickBot="1">
-      <c r="A10" s="12" t="s">
-        <v>670</v>
-      </c>
-      <c r="B10" s="28" t="str">
-        <f>VLOOKUP(A10,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Número de meses, dentro de los últimos 12 meses, en que no se registraron cargos.</v>
-      </c>
-      <c r="C10" s="28"/>
-    </row>
-    <row r="11" spans="1:3" ht="15" thickBot="1">
-      <c r="A11" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="B11" s="28" t="str">
-        <f>VLOOKUP(A11,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Cantidad total de alertas históricas relacionadas al cliente.</v>
-      </c>
-      <c r="C11" s="28"/>
-    </row>
-    <row r="12" spans="1:3" ht="15" thickBot="1">
-      <c r="A12" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="B12" s="28" t="str">
-        <f>VLOOKUP(A12,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Ratio de cantidad de abonos en efectivo respecto a la cantidad total de abonos, considerando ambos valores acumulados en los últimos 3 meses</v>
-      </c>
-      <c r="C12" s="28"/>
-    </row>
-    <row r="13" spans="1:3" ht="15" thickBot="1">
-      <c r="A13" s="12" t="s">
-        <v>643</v>
-      </c>
-      <c r="B13" s="28" t="str">
-        <f>VLOOKUP(A13,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Promedio de los cargos totales en los últimos 3 meses.</v>
-      </c>
-      <c r="C13" s="28"/>
-    </row>
-    <row r="14" spans="1:3" ht="15" thickBot="1">
-      <c r="A14" s="12" t="s">
-        <v>655</v>
-      </c>
-      <c r="B14" s="28" t="str">
-        <f>VLOOKUP(A14,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Porcentaje del monto de cargos realizados en efectivo sobre el total de cargos del último mes.</v>
-      </c>
-      <c r="C14" s="28"/>
-    </row>
-    <row r="15" spans="1:3" ht="15" thickBot="1">
-      <c r="A15" s="12" t="s">
-        <v>457</v>
-      </c>
-      <c r="B15" s="28" t="str">
-        <f>VLOOKUP(A15,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Ratio de cantida de abonos en efectivo respecto a la cantidad total de abonos, considerando ambos valores acumulados en el último mes.</v>
-      </c>
-      <c r="C15" s="28"/>
-    </row>
-    <row r="16" spans="1:3" ht="15" thickBot="1">
-      <c r="A16" s="12" t="s">
-        <v>894</v>
-      </c>
-      <c r="B16" s="28" t="str">
-        <f>VLOOKUP(A16,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Esta variable calcula la relación entre la cantidad de reportes de operaciones sospechosas (ROS) históricos y el número total de transacciones de egresos en los últimos 3 meses. Es un indicador de riesgo asociado a las operaciones recientes.</v>
-      </c>
-      <c r="C16" s="28"/>
-    </row>
-    <row r="17" spans="1:3" ht="15" thickBot="1">
-      <c r="A17" s="12" t="s">
-        <v>888</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>920</v>
-      </c>
-      <c r="C17" s="28"/>
-    </row>
-    <row r="18" spans="1:3" ht="15" thickBot="1">
-      <c r="A18" s="12" t="s">
-        <v>733</v>
-      </c>
-      <c r="B18" s="28" t="str">
-        <f>VLOOKUP(A18,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Monto total recibido desde el exterior en los últimos 12 meses.</v>
-      </c>
-      <c r="C18" s="28"/>
-    </row>
-    <row r="19" spans="1:3" ht="15" thickBot="1">
-      <c r="A19" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="B19" s="28" t="str">
-        <f>VLOOKUP(A19,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Esta variable mide la proporción de ingresos provenientes del exterior en relación con los ingresos totales (abonos) en los últimos 12 meses. Es un indicador de la dependencia de la empresa en ingresos internacionales.</v>
-      </c>
-      <c r="C19" s="28"/>
-    </row>
-    <row r="20" spans="1:3" ht="15" thickBot="1">
-      <c r="A20" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="B20" s="28" t="str">
-        <f>VLOOKUP(A20,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Monto máximo de egreso en un solo mes de una o más contrapartes dentro de los últimos 12 meses.</v>
-      </c>
-      <c r="C20" s="28"/>
-    </row>
-    <row r="21" spans="1:3" ht="15" thickBot="1">
-      <c r="A21" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="B21" s="28" t="str">
-        <f>VLOOKUP(A21,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Promedio mensual de egresos hacia contrapartes en los últimos 12 meses.</v>
-      </c>
-      <c r="C21" s="28"/>
-    </row>
-    <row r="22" spans="1:3" ht="15" thickBot="1">
-      <c r="A22" s="12" t="s">
-        <v>721</v>
-      </c>
-      <c r="B22" s="28" t="str">
-        <f>VLOOKUP(A22,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Monto total enviado al exterior en los últimos 12 meses.</v>
-      </c>
-      <c r="C22" s="28"/>
-    </row>
-    <row r="23" spans="1:3" ht="15" thickBot="1">
-      <c r="A23" s="27" t="s">
-        <v>895</v>
-      </c>
-      <c r="B23" s="28" t="str">
-        <f>VLOOKUP(A23,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Esta variable mide la proporción de ingresos provenientes del exterior en relación con los ingresos totales (abonos) en los últimos 12 meses. Es un indicador de la dependencia de la empresa en ingresos internacionales.</v>
-      </c>
-      <c r="C23" s="28"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" thickBot="1">
-      <c r="A24" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="B24" s="28" t="str">
-        <f>VLOOKUP(A24,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Número total de ROS en los que el cliente ha estado involucrado.</v>
-      </c>
-      <c r="C24" s="28"/>
-    </row>
-    <row r="25" spans="1:3" ht="15" thickBot="1">
-      <c r="A25" s="12" t="s">
-        <v>896</v>
-      </c>
-      <c r="B25" t="s">
-        <v>925</v>
-      </c>
-      <c r="C25" s="28"/>
-    </row>
-    <row r="26" spans="1:3" ht="15" thickBot="1">
-      <c r="A26" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="B26" s="28" t="str">
-        <f>VLOOKUP(A26,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Indicador si el cliente ha generado alguna alerta PLAFT en los últimos 12 meses.</v>
-      </c>
-      <c r="C26" s="28"/>
-    </row>
-    <row r="27" spans="1:3" ht="15" thickBot="1">
-      <c r="A27" s="12" t="s">
-        <v>850</v>
-      </c>
-      <c r="B27" s="28" t="str">
-        <f>VLOOKUP(A27,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Si el monto total abonos del último mes es mayor al monto promedio total abonos de los últimos 5 meses coloco 1, caso contrario 0</v>
-      </c>
-      <c r="C27" s="28"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" thickBot="1">
-      <c r="A28" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="B28" s="28" t="str">
-        <f>VLOOKUP(A28,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Promedio mensual de ingresos provenientes de suscontrapartes en los últimos 12 meses.</v>
-      </c>
-      <c r="C28" s="28"/>
-    </row>
-    <row r="29" spans="1:3" ht="15" thickBot="1">
-      <c r="A29" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B29" s="28" t="str">
-        <f>VLOOKUP(A29,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Número total de noticias negativas registradas del cliente.</v>
-      </c>
-      <c r="C29" s="28"/>
-    </row>
-    <row r="30" spans="1:3" ht="15" thickBot="1">
-      <c r="A30" s="12" t="s">
-        <v>890</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>924</v>
-      </c>
-      <c r="C30" s="28"/>
-    </row>
-    <row r="31" spans="1:3" ht="15" thickBot="1">
-      <c r="A31" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" s="28" t="str">
-        <f>VLOOKUP(A31,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Monto de facturación declarado del cliente, según SUNAT</v>
-      </c>
-      <c r="C31" s="28"/>
-    </row>
-    <row r="32" spans="1:3" ht="15" thickBot="1">
-      <c r="A32" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>921</v>
-      </c>
-      <c r="C32" s="28"/>
-    </row>
-    <row r="33" spans="1:3" ht="15" thickBot="1">
-      <c r="A33" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="28" t="str">
-        <f>VLOOKUP(A33,Diccionario!$C$7:$F$300,4,FALSE)</f>
-        <v>Identificador del sector asignado al cliente</v>
-      </c>
-      <c r="C33" s="28"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374C8810-FB16-41CA-85D2-70D0F0D810E2}">
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
